--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/CONNECTICUT_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/CONNECTICUT_2015.xlsx
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C175">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C522">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C543">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C876">
